--- a/澎湖店家確認表單.xlsx
+++ b/澎湖店家確認表單.xlsx
@@ -172,7 +172,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -180,16 +180,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -625,7 +615,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>完成率</t>
+          <t>發送率</t>
         </is>
       </c>
     </row>
@@ -3133,17 +3123,17 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>聯繫狀態</t>
+          <t>發送狀態</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>聯繫日期</t>
+          <t>發送日期</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>聯繫方式</t>
+          <t>發送方式</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -3221,7 +3211,7 @@
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J6" s="14" t="n"/>
@@ -3273,7 +3263,7 @@
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J7" s="14" t="n"/>
@@ -3321,7 +3311,7 @@
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J8" s="14" t="n"/>
@@ -3369,7 +3359,7 @@
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J9" s="14" t="n"/>
@@ -3417,7 +3407,7 @@
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J10" s="14" t="n"/>
@@ -3465,7 +3455,7 @@
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J11" s="14" t="n"/>
@@ -3513,7 +3503,7 @@
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J12" s="14" t="n"/>
@@ -3565,7 +3555,7 @@
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J13" s="14" t="n"/>
@@ -3617,7 +3607,7 @@
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J14" s="14" t="n"/>
@@ -3725,7 +3715,7 @@
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J16" s="14" t="n"/>
@@ -3785,7 +3775,7 @@
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J17" s="14" t="n"/>
@@ -4477,7 +4467,7 @@
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J31" s="14" t="n"/>
@@ -4525,7 +4515,7 @@
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J32" s="14" t="n"/>
@@ -4573,7 +4563,7 @@
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J33" s="14" t="n"/>
@@ -4621,7 +4611,7 @@
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J34" s="14" t="n"/>
@@ -4981,7 +4971,7 @@
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J41" s="14" t="n"/>
@@ -5193,7 +5183,7 @@
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J45" s="14" t="n"/>
@@ -5401,7 +5391,7 @@
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J49" s="14" t="n"/>
@@ -5457,7 +5447,7 @@
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J50" s="14" t="n"/>
@@ -5641,7 +5631,7 @@
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J54" s="14" t="n"/>
@@ -5689,7 +5679,7 @@
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J55" s="14" t="n"/>
@@ -5737,7 +5727,7 @@
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J56" s="14" t="n"/>
@@ -5785,7 +5775,7 @@
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J57" s="14" t="n"/>
@@ -5833,7 +5823,7 @@
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J58" s="14" t="n"/>
@@ -5881,7 +5871,7 @@
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J59" s="14" t="n"/>
@@ -6685,7 +6675,7 @@
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J75" s="14" t="n"/>
@@ -6737,7 +6727,7 @@
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J76" s="14" t="n"/>
@@ -6785,7 +6775,7 @@
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J77" s="14" t="n"/>
@@ -6837,7 +6827,7 @@
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J78" s="14" t="n"/>
@@ -6885,7 +6875,7 @@
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J79" s="14" t="n"/>
@@ -6933,7 +6923,7 @@
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J80" s="14" t="n"/>
@@ -6981,7 +6971,7 @@
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J81" s="14" t="n"/>
@@ -7029,7 +7019,7 @@
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J82" s="14" t="n"/>
@@ -7081,7 +7071,7 @@
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J83" s="14" t="n"/>
@@ -7133,7 +7123,7 @@
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J84" s="14" t="n"/>
@@ -7193,7 +7183,7 @@
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J85" s="14" t="n"/>
@@ -7249,7 +7239,7 @@
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J86" s="14" t="n"/>
@@ -7305,7 +7295,7 @@
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J87" s="14" t="n"/>
@@ -7385,7 +7375,7 @@
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J89" s="14" t="n"/>
@@ -7441,7 +7431,7 @@
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J90" s="14" t="n"/>
@@ -7493,7 +7483,7 @@
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J91" s="14" t="n"/>
@@ -7541,7 +7531,7 @@
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J92" s="14" t="n"/>
@@ -7589,7 +7579,7 @@
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J93" s="14" t="n"/>
@@ -7637,7 +7627,7 @@
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J94" s="14" t="n"/>
@@ -7685,7 +7675,7 @@
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J95" s="14" t="n"/>
@@ -7733,7 +7723,7 @@
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J96" s="14" t="n"/>
@@ -7781,7 +7771,7 @@
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J97" s="14" t="n"/>
@@ -7833,7 +7823,7 @@
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J98" s="14" t="n"/>
@@ -7889,7 +7879,7 @@
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J99" s="14" t="n"/>
@@ -7945,7 +7935,7 @@
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J100" s="14" t="n"/>
@@ -8073,7 +8063,7 @@
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J103" s="14" t="n"/>
@@ -8169,7 +8159,7 @@
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J105" s="14" t="n"/>
@@ -8217,7 +8207,7 @@
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J106" s="14" t="n"/>
@@ -8265,7 +8255,7 @@
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J107" s="14" t="n"/>
@@ -8313,7 +8303,7 @@
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J108" s="14" t="n"/>
@@ -8409,7 +8399,7 @@
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J110" s="14" t="n"/>
@@ -8457,7 +8447,7 @@
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J111" s="14" t="n"/>
@@ -8505,7 +8495,7 @@
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J112" s="14" t="n"/>
@@ -8553,7 +8543,7 @@
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J113" s="14" t="n"/>
@@ -8605,7 +8595,7 @@
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J114" s="14" t="n"/>
@@ -8681,7 +8671,7 @@
       </c>
       <c r="I116" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J116" s="14" t="n"/>
@@ -8729,7 +8719,7 @@
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J117" s="14" t="n"/>
@@ -8777,7 +8767,7 @@
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J118" s="14" t="n"/>
@@ -8825,7 +8815,7 @@
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J119" s="14" t="n"/>
@@ -8873,7 +8863,7 @@
       </c>
       <c r="I120" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J120" s="14" t="n"/>
@@ -9129,7 +9119,7 @@
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J125" s="14" t="n"/>
@@ -9314,7 +9304,7 @@
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J129" s="14" t="n"/>
@@ -9366,7 +9356,7 @@
       </c>
       <c r="I130" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J130" s="14" t="n"/>
@@ -9414,7 +9404,7 @@
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J131" s="14" t="n"/>
@@ -9462,7 +9452,7 @@
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J132" s="14" t="n"/>
@@ -9510,7 +9500,7 @@
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J133" s="14" t="n"/>
@@ -9558,7 +9548,7 @@
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J134" s="14" t="n"/>
@@ -9674,7 +9664,7 @@
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J136" s="14" t="n"/>
@@ -9734,7 +9724,7 @@
       </c>
       <c r="I137" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J137" s="14" t="n"/>
@@ -9846,7 +9836,7 @@
       </c>
       <c r="I139" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J139" s="14" t="n"/>
@@ -9918,7 +9908,7 @@
       </c>
       <c r="I141" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J141" s="14" t="n"/>
@@ -9970,7 +9960,7 @@
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J142" s="14" t="n"/>
@@ -10018,7 +10008,7 @@
       </c>
       <c r="I143" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J143" s="14" t="n"/>
@@ -10066,7 +10056,7 @@
       </c>
       <c r="I144" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J144" s="14" t="n"/>
@@ -10114,7 +10104,7 @@
       </c>
       <c r="I145" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J145" s="14" t="n"/>
@@ -10162,7 +10152,7 @@
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J146" s="14" t="n"/>
@@ -10210,7 +10200,7 @@
       </c>
       <c r="I147" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J147" s="14" t="n"/>
@@ -10258,7 +10248,7 @@
       </c>
       <c r="I148" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J148" s="14" t="n"/>
@@ -10310,7 +10300,7 @@
       </c>
       <c r="I149" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J149" s="14" t="n"/>
@@ -10362,7 +10352,7 @@
       </c>
       <c r="I150" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J150" s="14" t="n"/>
@@ -10430,7 +10420,7 @@
       </c>
       <c r="I152" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J152" s="14" t="n"/>
@@ -10478,7 +10468,7 @@
       </c>
       <c r="I153" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J153" s="14" t="n"/>
@@ -10526,7 +10516,7 @@
       </c>
       <c r="I154" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J154" s="14" t="n"/>
@@ -10578,7 +10568,7 @@
       </c>
       <c r="I155" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J155" s="14" t="n"/>
@@ -10634,7 +10624,7 @@
       </c>
       <c r="I156" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J156" s="14" t="n"/>
@@ -10966,7 +10956,7 @@
       </c>
       <c r="I163" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J163" s="14" t="n"/>
@@ -11022,7 +11012,7 @@
       </c>
       <c r="I164" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J164" s="14" t="n"/>
@@ -11070,7 +11060,7 @@
       </c>
       <c r="I165" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J165" s="14" t="n"/>
@@ -11118,7 +11108,7 @@
       </c>
       <c r="I166" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J166" s="14" t="n"/>
@@ -11166,7 +11156,7 @@
       </c>
       <c r="I167" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J167" s="14" t="n"/>
@@ -11214,7 +11204,7 @@
       </c>
       <c r="I168" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J168" s="14" t="n"/>
@@ -11266,7 +11256,7 @@
       </c>
       <c r="I169" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J169" s="14" t="n"/>
@@ -11314,7 +11304,7 @@
       </c>
       <c r="I170" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J170" s="14" t="n"/>
@@ -11386,7 +11376,7 @@
       </c>
       <c r="I172" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J172" s="14" t="n"/>
@@ -11434,7 +11424,7 @@
       </c>
       <c r="I173" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J173" s="14" t="n"/>
@@ -11482,7 +11472,7 @@
       </c>
       <c r="I174" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J174" s="14" t="n"/>
@@ -11762,7 +11752,7 @@
       </c>
       <c r="I180" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J180" s="14" t="n"/>
@@ -11810,7 +11800,7 @@
       </c>
       <c r="I181" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J181" s="14" t="n"/>
@@ -11858,7 +11848,7 @@
       </c>
       <c r="I182" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J182" s="14" t="n"/>
@@ -11906,7 +11896,7 @@
       </c>
       <c r="I183" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J183" s="14" t="n"/>
@@ -12062,7 +12052,7 @@
       </c>
       <c r="I186" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J186" s="14" t="n"/>
@@ -12138,7 +12128,7 @@
       </c>
       <c r="I188" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J188" s="14" t="n"/>
@@ -12238,7 +12228,7 @@
       </c>
       <c r="I190" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J190" s="14" t="n"/>
@@ -12342,7 +12332,7 @@
       </c>
       <c r="I192" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J192" s="14" t="n"/>
@@ -12398,7 +12388,7 @@
       </c>
       <c r="I193" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J193" s="14" t="n"/>
@@ -12674,7 +12664,7 @@
       </c>
       <c r="I199" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J199" s="14" t="n"/>
@@ -12746,7 +12736,7 @@
       </c>
       <c r="I201" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J201" s="14" t="n"/>
@@ -12794,7 +12784,7 @@
       </c>
       <c r="I202" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J202" s="14" t="n"/>
@@ -12842,7 +12832,7 @@
       </c>
       <c r="I203" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J203" s="14" t="n"/>
@@ -12890,7 +12880,7 @@
       </c>
       <c r="I204" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J204" s="14" t="n"/>
@@ -12942,7 +12932,7 @@
       </c>
       <c r="I205" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J205" s="14" t="n"/>
@@ -13010,7 +13000,7 @@
       </c>
       <c r="I207" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J207" s="14" t="n"/>
@@ -13062,7 +13052,7 @@
       </c>
       <c r="I208" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J208" s="14" t="n"/>
@@ -13114,7 +13104,7 @@
       </c>
       <c r="I209" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J209" s="14" t="n"/>
@@ -13166,7 +13156,7 @@
       </c>
       <c r="I210" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J210" s="14" t="n"/>
@@ -13222,7 +13212,7 @@
       </c>
       <c r="I211" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J211" s="14" t="n"/>
@@ -13354,7 +13344,7 @@
       </c>
       <c r="I214" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J214" s="14" t="n"/>
@@ -13406,7 +13396,7 @@
       </c>
       <c r="I215" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J215" s="14" t="n"/>
@@ -13462,7 +13452,7 @@
       </c>
       <c r="I216" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J216" s="14" t="n"/>
@@ -13766,7 +13756,7 @@
       </c>
       <c r="I223" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J223" s="14" t="n"/>
@@ -13866,7 +13856,7 @@
       </c>
       <c r="I225" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J225" s="14" t="n"/>
@@ -13994,7 +13984,7 @@
       </c>
       <c r="I228" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J228" s="14" t="n"/>
@@ -14042,7 +14032,7 @@
       </c>
       <c r="I229" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J229" s="14" t="n"/>
@@ -14222,7 +14212,7 @@
       </c>
       <c r="I233" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J233" s="14" t="n"/>
@@ -14270,7 +14260,7 @@
       </c>
       <c r="I234" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J234" s="14" t="n"/>
@@ -14318,7 +14308,7 @@
       </c>
       <c r="I235" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J235" s="14" t="n"/>
@@ -14386,7 +14376,7 @@
       </c>
       <c r="I237" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J237" s="14" t="n"/>
@@ -14434,7 +14424,7 @@
       </c>
       <c r="I238" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J238" s="14" t="n"/>
@@ -14482,7 +14472,7 @@
       </c>
       <c r="I239" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J239" s="14" t="n"/>
@@ -14554,7 +14544,7 @@
       </c>
       <c r="I241" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J241" s="14" t="n"/>
@@ -14602,7 +14592,7 @@
       </c>
       <c r="I242" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J242" s="14" t="n"/>
@@ -14650,7 +14640,7 @@
       </c>
       <c r="I243" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J243" s="14" t="n"/>
@@ -14718,7 +14708,7 @@
       </c>
       <c r="I245" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J245" s="14" t="n"/>
@@ -14766,7 +14756,7 @@
       </c>
       <c r="I246" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J246" s="14" t="n"/>
@@ -14822,7 +14812,7 @@
       </c>
       <c r="I247" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J247" s="14" t="n"/>
@@ -14894,7 +14884,7 @@
       </c>
       <c r="I249" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J249" s="14" t="n"/>
@@ -14942,7 +14932,7 @@
       </c>
       <c r="I250" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J250" s="14" t="n"/>
@@ -14998,7 +14988,7 @@
       </c>
       <c r="I251" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J251" s="14" t="n"/>
@@ -15114,7 +15104,7 @@
       </c>
       <c r="I254" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J254" s="14" t="n"/>
@@ -15162,7 +15152,7 @@
       </c>
       <c r="I255" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J255" s="14" t="n"/>
@@ -15230,7 +15220,7 @@
       </c>
       <c r="I257" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J257" s="14" t="n"/>
@@ -15278,7 +15268,7 @@
       </c>
       <c r="I258" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J258" s="14" t="n"/>
@@ -15398,7 +15388,7 @@
       </c>
       <c r="I261" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J261" s="14" t="n"/>
@@ -15578,7 +15568,7 @@
       </c>
       <c r="I265" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J265" s="14" t="n"/>
@@ -15626,7 +15616,7 @@
       </c>
       <c r="I266" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J266" s="14" t="n"/>
@@ -15686,7 +15676,7 @@
       </c>
       <c r="I267" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J267" s="14" t="n"/>
@@ -15754,7 +15744,7 @@
       </c>
       <c r="I269" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J269" s="14" t="n"/>
@@ -15802,7 +15792,7 @@
       </c>
       <c r="I270" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J270" s="14" t="n"/>
@@ -15850,7 +15840,7 @@
       </c>
       <c r="I271" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J271" s="14" t="n"/>
@@ -15918,7 +15908,7 @@
       </c>
       <c r="I273" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J273" s="14" t="n"/>
@@ -15970,7 +15960,7 @@
       </c>
       <c r="I274" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J274" s="14" t="n"/>
@@ -16018,7 +16008,7 @@
       </c>
       <c r="I275" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J275" s="14" t="n"/>
@@ -16146,7 +16136,7 @@
       </c>
       <c r="I278" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J278" s="14" t="n"/>
@@ -16198,7 +16188,7 @@
       </c>
       <c r="I279" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J279" s="14" t="n"/>
@@ -16330,7 +16320,7 @@
       </c>
       <c r="I282" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J282" s="14" t="n"/>
@@ -16398,7 +16388,7 @@
       </c>
       <c r="I284" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J284" s="14" t="n"/>
@@ -16446,7 +16436,7 @@
       </c>
       <c r="I285" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J285" s="14" t="n"/>
@@ -16514,7 +16504,7 @@
       </c>
       <c r="I287" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J287" s="14" t="n"/>
@@ -16638,7 +16628,7 @@
       </c>
       <c r="I290" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J290" s="14" t="n"/>
@@ -16686,7 +16676,7 @@
       </c>
       <c r="I291" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J291" s="14" t="n"/>
@@ -16754,7 +16744,7 @@
       </c>
       <c r="I293" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J293" s="14" t="n"/>
@@ -16802,7 +16792,7 @@
       </c>
       <c r="I294" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J294" s="14" t="n"/>
@@ -16870,7 +16860,7 @@
       </c>
       <c r="I296" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J296" s="14" t="n"/>
@@ -16918,7 +16908,7 @@
       </c>
       <c r="I297" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J297" s="14" t="n"/>
@@ -16986,7 +16976,7 @@
       </c>
       <c r="I299" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J299" s="14" t="n"/>
@@ -17034,7 +17024,7 @@
       </c>
       <c r="I300" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J300" s="14" t="n"/>
@@ -17102,7 +17092,7 @@
       </c>
       <c r="I302" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J302" s="14" t="n"/>
@@ -17222,7 +17212,7 @@
       </c>
       <c r="I305" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J305" s="14" t="n"/>
@@ -17270,7 +17260,7 @@
       </c>
       <c r="I306" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J306" s="14" t="n"/>
@@ -17338,7 +17328,7 @@
       </c>
       <c r="I308" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J308" s="14" t="n"/>
@@ -17386,7 +17376,7 @@
       </c>
       <c r="I309" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J309" s="14" t="n"/>
@@ -17454,7 +17444,7 @@
       </c>
       <c r="I311" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J311" s="14" t="n"/>
@@ -17578,7 +17568,7 @@
       </c>
       <c r="I314" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J314" s="14" t="n"/>
@@ -17626,7 +17616,7 @@
       </c>
       <c r="I315" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J315" s="14" t="n"/>
@@ -17818,7 +17808,7 @@
       </c>
       <c r="I320" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J320" s="14" t="n"/>
@@ -17894,7 +17884,7 @@
       </c>
       <c r="I322" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J322" s="14" t="n"/>
@@ -17966,7 +17956,7 @@
       </c>
       <c r="I324" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J324" s="14" t="n"/>
@@ -18034,7 +18024,7 @@
       </c>
       <c r="I326" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J326" s="14" t="n"/>
@@ -18106,7 +18096,7 @@
       </c>
       <c r="I328" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J328" s="14" t="n"/>
@@ -18174,7 +18164,7 @@
       </c>
       <c r="I330" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J330" s="14" t="n"/>
@@ -18246,7 +18236,7 @@
       </c>
       <c r="I332" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J332" s="14" t="n"/>
@@ -18314,7 +18304,7 @@
       </c>
       <c r="I334" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J334" s="14" t="n"/>
@@ -18382,7 +18372,7 @@
       </c>
       <c r="I336" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J336" s="14" t="n"/>
@@ -18450,7 +18440,7 @@
       </c>
       <c r="I338" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J338" s="14" t="n"/>
@@ -18518,7 +18508,7 @@
       </c>
       <c r="I340" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J340" s="14" t="n"/>
@@ -18586,7 +18576,7 @@
       </c>
       <c r="I342" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J342" s="14" t="n"/>
@@ -18722,7 +18712,7 @@
       </c>
       <c r="I346" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J346" s="14" t="n"/>
@@ -18794,7 +18784,7 @@
       </c>
       <c r="I348" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J348" s="14" t="n"/>
@@ -18866,7 +18856,7 @@
       </c>
       <c r="I350" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J350" s="14" t="n"/>
@@ -18943,7 +18933,7 @@
       </c>
       <c r="I352" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J352" s="14" t="n"/>
@@ -19011,7 +19001,7 @@
       </c>
       <c r="I354" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J354" s="14" t="n"/>
@@ -19079,7 +19069,7 @@
       </c>
       <c r="I356" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J356" s="14" t="n"/>
@@ -19147,7 +19137,7 @@
       </c>
       <c r="I358" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J358" s="14" t="n"/>
@@ -19219,7 +19209,7 @@
       </c>
       <c r="I360" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J360" s="14" t="n"/>
@@ -19287,7 +19277,7 @@
       </c>
       <c r="I362" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J362" s="14" t="n"/>
@@ -19355,7 +19345,7 @@
       </c>
       <c r="I364" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J364" s="14" t="n"/>
@@ -19423,7 +19413,7 @@
       </c>
       <c r="I366" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J366" s="14" t="n"/>
@@ -19491,7 +19481,7 @@
       </c>
       <c r="I368" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J368" s="14" t="n"/>
@@ -19559,7 +19549,7 @@
       </c>
       <c r="I370" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J370" s="14" t="n"/>
@@ -19859,7 +19849,7 @@
       </c>
       <c r="I377" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J377" s="14" t="n"/>
@@ -20267,7 +20257,7 @@
       </c>
       <c r="I386" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J386" s="14" t="n"/>
@@ -20339,7 +20329,7 @@
       </c>
       <c r="I388" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J388" s="14" t="n"/>
@@ -20459,7 +20449,7 @@
       </c>
       <c r="I391" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J391" s="14" t="n"/>
@@ -20527,7 +20517,7 @@
       </c>
       <c r="I393" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J393" s="14" t="n"/>
@@ -20603,7 +20593,7 @@
       </c>
       <c r="I395" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J395" s="14" t="n"/>
@@ -20675,7 +20665,7 @@
       </c>
       <c r="I397" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J397" s="14" t="n"/>
@@ -20743,7 +20733,7 @@
       </c>
       <c r="I399" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J399" s="14" t="n"/>
@@ -20967,7 +20957,7 @@
       </c>
       <c r="I405" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J405" s="14" t="n"/>
@@ -21019,7 +21009,7 @@
       </c>
       <c r="I406" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J406" s="14" t="n"/>
@@ -21071,7 +21061,7 @@
       </c>
       <c r="I407" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J407" s="14" t="n"/>
@@ -21147,7 +21137,7 @@
       </c>
       <c r="I409" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J409" s="14" t="n"/>
@@ -21219,7 +21209,7 @@
       </c>
       <c r="I411" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J411" s="14" t="n"/>
@@ -21287,7 +21277,7 @@
       </c>
       <c r="I413" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J413" s="14" t="n"/>
@@ -21427,7 +21417,7 @@
       </c>
       <c r="I417" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J417" s="14" t="n"/>
@@ -21499,7 +21489,7 @@
       </c>
       <c r="I419" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J419" s="14" t="n"/>
@@ -21575,7 +21565,7 @@
       </c>
       <c r="I421" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J421" s="14" t="n"/>
@@ -21627,7 +21617,7 @@
       </c>
       <c r="I422" s="13" t="inlineStr">
         <is>
-          <t>未聯繫</t>
+          <t>未發送</t>
         </is>
       </c>
       <c r="J422" s="14" t="n"/>
@@ -21734,18 +21724,15 @@
   </mergeCells>
   <conditionalFormatting sqref="I6:I29 I31:I52 I54:I73 I75:I87 I89:I101 I103:I114 I116:I127 I129:I139 I141:I150 I152:I161 I163:I170 I172:I178 I180:I186 I188:I193 I195:I199 I201:I205 I207:I211 I213:I216 I218:I221 I223:I226 I228:I231 I233:I235 I237:I239 I241:I243 I245:I247 I249:I251 I253:I255 I257:I259 I261:I263 I265:I267 I269:I271 I273:I275 I277:I279 I281:I282 I284:I285 I287:I288 I290:I291 I293:I294 I296:I297 I299:I300 I302:I303 I305:I306 I308:I309 I311:I312 I314:I315 I317:I318 I320 I322 I324 I326 I328 I330 I332 I334 I336 I338 I340 I342 I344 I346 I348 I350 I352 I354 I356 I358 I360 I362 I364 I366 I368 I370:I371 I373 I375:I378 I380:I383 I385:I386 I388:I389 I391 I393 I395 I397 I399 I401 I403 I405:I407 I409 I411 I413 I415 I417 I419 I421:I422">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
-      <formula>"已合作"</formula>
+      <formula>"已發送"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
-      <formula>"婉拒"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
-      <formula>"聯繫不上"</formula>
+      <formula>"未發送"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="I6:I29 I31:I52 I54:I73 I75:I87 I89:I101 I103:I114 I116:I127 I129:I139 I141:I150 I152:I161 I163:I170 I172:I178 I180:I186 I188:I193 I195:I199 I201:I205 I207:I211 I213:I216 I218:I221 I223:I226 I228:I231 I233:I235 I237:I239 I241:I243 I245:I247 I249:I251 I253:I255 I257:I259 I261:I263 I265:I267 I269:I271 I273:I275 I277:I279 I281:I282 I284:I285 I287:I288 I290:I291 I293:I294 I296:I297 I299:I300 I302:I303 I305:I306 I308:I309 I311:I312 I314:I315 I317:I318 I320 I322 I324 I326 I328 I330 I332 I334 I336 I338 I340 I342 I344 I346 I348 I350 I352 I354 I356 I358 I360 I362 I364 I366 I368 I370:I371 I373 I375:I378 I380:I383 I385:I386 I388:I389 I391 I393 I395 I397 I399 I401 I403 I405:I407 I409 I411 I413 I415 I417 I419 I421:I422" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"未聯繫,已發送,已回覆,已合作,婉拒,聯繫不上"</formula1>
+      <formula1>"未發送,已發送"</formula1>
     </dataValidation>
     <dataValidation sqref="K6:K29 K31:K52 K54:K73 K75:K87 K89:K101 K103:K114 K116:K127 K129:K139 K141:K150 K152:K161 K163:K170 K172:K178 K180:K186 K188:K193 K195:K199 K201:K205 K207:K211 K213:K216 K218:K221 K223:K226 K228:K231 K233:K235 K237:K239 K241:K243 K245:K247 K249:K251 K253:K255 K257:K259 K261:K263 K265:K267 K269:K271 K273:K275 K277:K279 K281:K282 K284:K285 K287:K288 K290:K291 K293:K294 K296:K297 K299:K300 K302:K303 K305:K306 K308:K309 K311:K312 K314:K315 K317:K318 K320 K322 K324 K326 K328 K330 K332 K334 K336 K338 K340 K342 K344 K346 K348 K350 K352 K354 K356 K358 K360 K362 K364 K366 K368 K370:K371 K373 K375:K378 K380:K383 K385:K386 K388:K389 K391 K393 K395 K397 K399 K401 K403 K405:K407 K409 K411 K413 K415 K417 K419 K421:K422" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"現場拜訪,電話,LINE,Email,FB/IG 私訊"</formula1>
@@ -21809,7 +21796,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>聯繫狀態</t>
+          <t>發送狀態</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -23038,7 +23025,7 @@
   <autoFilter ref="A4:F80"/>
   <dataValidations count="1">
     <dataValidation sqref="E5:E80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"未聯繫,已發送,已回覆,已合作,婉拒,聯繫不上"</formula1>
+      <formula1>"未發送,已發送"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/澎湖店家確認表單.xlsx
+++ b/澎湖店家確認表單.xlsx
@@ -172,7 +172,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -180,6 +180,16 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -21724,15 +21734,18 @@
   </mergeCells>
   <conditionalFormatting sqref="I6:I29 I31:I52 I54:I73 I75:I87 I89:I101 I103:I114 I116:I127 I129:I139 I141:I150 I152:I161 I163:I170 I172:I178 I180:I186 I188:I193 I195:I199 I201:I205 I207:I211 I213:I216 I218:I221 I223:I226 I228:I231 I233:I235 I237:I239 I241:I243 I245:I247 I249:I251 I253:I255 I257:I259 I261:I263 I265:I267 I269:I271 I273:I275 I277:I279 I281:I282 I284:I285 I287:I288 I290:I291 I293:I294 I296:I297 I299:I300 I302:I303 I305:I306 I308:I309 I311:I312 I314:I315 I317:I318 I320 I322 I324 I326 I328 I330 I332 I334 I336 I338 I340 I342 I344 I346 I348 I350 I352 I354 I356 I358 I360 I362 I364 I366 I368 I370:I371 I373 I375:I378 I380:I383 I385:I386 I388:I389 I391 I393 I395 I397 I399 I401 I403 I405:I407 I409 I411 I413 I415 I417 I419 I421:I422">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"已張貼"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
       <formula>"已發送"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"未發送"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="I6:I29 I31:I52 I54:I73 I75:I87 I89:I101 I103:I114 I116:I127 I129:I139 I141:I150 I152:I161 I163:I170 I172:I178 I180:I186 I188:I193 I195:I199 I201:I205 I207:I211 I213:I216 I218:I221 I223:I226 I228:I231 I233:I235 I237:I239 I241:I243 I245:I247 I249:I251 I253:I255 I257:I259 I261:I263 I265:I267 I269:I271 I273:I275 I277:I279 I281:I282 I284:I285 I287:I288 I290:I291 I293:I294 I296:I297 I299:I300 I302:I303 I305:I306 I308:I309 I311:I312 I314:I315 I317:I318 I320 I322 I324 I326 I328 I330 I332 I334 I336 I338 I340 I342 I344 I346 I348 I350 I352 I354 I356 I358 I360 I362 I364 I366 I368 I370:I371 I373 I375:I378 I380:I383 I385:I386 I388:I389 I391 I393 I395 I397 I399 I401 I403 I405:I407 I409 I411 I413 I415 I417 I419 I421:I422" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"未發送,已發送"</formula1>
+      <formula1>"未發送,已發送,已張貼"</formula1>
     </dataValidation>
     <dataValidation sqref="K6:K29 K31:K52 K54:K73 K75:K87 K89:K101 K103:K114 K116:K127 K129:K139 K141:K150 K152:K161 K163:K170 K172:K178 K180:K186 K188:K193 K195:K199 K201:K205 K207:K211 K213:K216 K218:K221 K223:K226 K228:K231 K233:K235 K237:K239 K241:K243 K245:K247 K249:K251 K253:K255 K257:K259 K261:K263 K265:K267 K269:K271 K273:K275 K277:K279 K281:K282 K284:K285 K287:K288 K290:K291 K293:K294 K296:K297 K299:K300 K302:K303 K305:K306 K308:K309 K311:K312 K314:K315 K317:K318 K320 K322 K324 K326 K328 K330 K332 K334 K336 K338 K340 K342 K344 K346 K348 K350 K352 K354 K356 K358 K360 K362 K364 K366 K368 K370:K371 K373 K375:K378 K380:K383 K385:K386 K388:K389 K391 K393 K395 K397 K399 K401 K403 K405:K407 K409 K411 K413 K415 K417 K419 K421:K422" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"現場拜訪,電話,LINE,Email,FB/IG 私訊"</formula1>
@@ -23025,7 +23038,7 @@
   <autoFilter ref="A4:F80"/>
   <dataValidations count="1">
     <dataValidation sqref="E5:E80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"未發送,已發送"</formula1>
+      <formula1>"未發送,已發送,已張貼"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
